--- a/corpus/C08.xlsx
+++ b/corpus/C08.xlsx
@@ -751,77 +751,76 @@
         <f>G9</f>
         <v>9370.0</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
+        <v>7900</v>
+      </c>
+      <c r="J5">
         <f>H9</f>
         <v>9695.0</v>
       </c>
-      <c r="J5">
-        <f>I9</f>
-        <v>10031.0</v>
-      </c>
       <c r="K5">
         <f>J9</f>
-        <v>10379.0</v>
+        <v>10031.0</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>10739.0</v>
+        <v>10379.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>11112.0</v>
+        <v>10739.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>11497.0</v>
+        <v>11112.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>11896.0</v>
+        <v>11497.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>12309.0</v>
+        <v>11896.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>12736.0</v>
+        <v>12309.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>13178.0</v>
+        <v>12736.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>13635.0</v>
+        <v>13178.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>14108.0</v>
+        <v>13635.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>14598.0</v>
+        <v>14108.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>15104.0</v>
+        <v>14598.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>15628.0</v>
+        <v>15104.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>16170.0</v>
+        <v>15628.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>16731.0</v>
+        <v>16170.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>17312.0</v>
+        <v>16731.0</v>
       </c>
     </row>
     <row r="6">
@@ -856,75 +855,75 @@
       </c>
       <c r="I6">
         <f>ROUND(I5*Assumptions!$B$5,0)</f>
-        <v>507.0</v>
+        <v>413.0</v>
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$5,0)</f>
-        <v>525.0</v>
+        <v>507.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>543.0</v>
+        <v>525.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>562.0</v>
+        <v>543.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>581.0</v>
+        <v>562.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>601.0</v>
+        <v>581.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>622.0</v>
+        <v>601.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>644.0</v>
+        <v>622.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>666.0</v>
+        <v>644.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>689.0</v>
+        <v>666.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>713.0</v>
+        <v>689.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>738.0</v>
+        <v>713.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>763.0</v>
+        <v>738.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>790.0</v>
+        <v>763.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>817.0</v>
+        <v>790.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>846.0</v>
+        <v>817.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>875.0</v>
+        <v>846.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>905.0</v>
+        <v>875.0</v>
       </c>
     </row>
     <row r="7">
@@ -959,75 +958,75 @@
       </c>
       <c r="I7">
         <f>-ROUND(I5*Assumptions!$B$6,0)</f>
-        <v>-171.0</v>
+        <v>-139.0</v>
       </c>
       <c r="J7">
         <f>-ROUND(J5*Assumptions!$B$6,0)</f>
-        <v>-177.0</v>
+        <v>-171.0</v>
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-183.0</v>
+        <v>-177.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-189.0</v>
+        <v>-183.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-196.0</v>
+        <v>-189.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-202.0</v>
+        <v>-196.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-209.0</v>
+        <v>-202.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-217.0</v>
+        <v>-209.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-224.0</v>
+        <v>-217.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-232.0</v>
+        <v>-224.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-240.0</v>
+        <v>-232.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-248.0</v>
+        <v>-240.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-257.0</v>
+        <v>-248.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-266.0</v>
+        <v>-257.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-275.0</v>
+        <v>-266.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-285.0</v>
+        <v>-275.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-294.0</v>
+        <v>-285.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-305.0</v>
+        <v>-294.0</v>
       </c>
     </row>
     <row r="9">
@@ -1062,75 +1061,75 @@
       </c>
       <c r="I9">
         <f>I5+I6+I7</f>
-        <v>10031.0</v>
+        <v>8174.0</v>
       </c>
       <c r="J9">
         <f>J5+J6+J7</f>
-        <v>10379.0</v>
+        <v>10031.0</v>
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>10739.0</v>
+        <v>10379.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>11112.0</v>
+        <v>10739.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>11497.0</v>
+        <v>11112.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>11896.0</v>
+        <v>11497.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>12309.0</v>
+        <v>11896.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>12736.0</v>
+        <v>12309.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>13178.0</v>
+        <v>12736.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>13635.0</v>
+        <v>13178.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>14108.0</v>
+        <v>13635.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>14598.0</v>
+        <v>14108.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>15104.0</v>
+        <v>14598.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>15628.0</v>
+        <v>15104.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>16170.0</v>
+        <v>15628.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>16731.0</v>
+        <v>16170.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>17312.0</v>
+        <v>16731.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>17912.0</v>
+        <v>17312.0</v>
       </c>
     </row>
     <row r="11">
@@ -1268,75 +1267,75 @@
       </c>
       <c r="I13">
         <f>ROUND((I5+I9)/2,0)</f>
-        <v>9863.0</v>
+        <v>8037.0</v>
       </c>
       <c r="J13">
         <f>ROUND((J5+J9)/2,0)</f>
-        <v>10205.0</v>
+        <v>9863.0</v>
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>10559.0</v>
+        <v>10205.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>10926.0</v>
+        <v>10559.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>11305.0</v>
+        <v>10926.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>11697.0</v>
+        <v>11305.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>12103.0</v>
+        <v>11697.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>12523.0</v>
+        <v>12103.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>12957.0</v>
+        <v>12523.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>13407.0</v>
+        <v>12957.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>13872.0</v>
+        <v>13407.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>14353.0</v>
+        <v>13872.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>14851.0</v>
+        <v>14353.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>15366.0</v>
+        <v>14851.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>15899.0</v>
+        <v>15366.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>16451.0</v>
+        <v>15899.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>17022.0</v>
+        <v>16451.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>17612.0</v>
+        <v>17022.0</v>
       </c>
     </row>
     <row r="15">
@@ -1371,75 +1370,75 @@
       </c>
       <c r="I15">
         <f>ROUND(I13*I11,0)</f>
-        <v>794761.0</v>
+        <v>647621.0</v>
       </c>
       <c r="J15">
         <f>ROUND(J13*J11,0)</f>
-        <v>828442.0</v>
+        <v>800678.0</v>
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>863515.0</v>
+        <v>834565.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>900193.0</v>
+        <v>869956.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>938315.0</v>
+        <v>906858.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>977986.0</v>
+        <v>945211.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>1019436.0</v>
+        <v>985238.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>1062577.0</v>
+        <v>1026940.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>1107564.0</v>
+        <v>1070466.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>1154477.0</v>
+        <v>1115727.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>1203396.0</v>
+        <v>1163057.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>1254309.0</v>
+        <v>1212274.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>1307482.0</v>
+        <v>1263638.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>1362811.0</v>
+        <v>1317135.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>1420576.0</v>
+        <v>1372952.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>1480755.0</v>
+        <v>1431069.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>1543555.0</v>
+        <v>1491777.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>1608856.0</v>
+        <v>1554960.0</v>
       </c>
     </row>
     <row r="17">
@@ -1474,75 +1473,75 @@
       </c>
       <c r="I17">
         <f>H17+I15</f>
-        <v>4929364.0</v>
+        <v>4782224.0</v>
       </c>
       <c r="J17">
         <f>I17+J15</f>
-        <v>5757806.0</v>
+        <v>5582902.0</v>
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>6621321.0</v>
+        <v>6417467.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>7521514.0</v>
+        <v>7287423.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>8459829.0</v>
+        <v>8194281.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>9437815.0</v>
+        <v>9139492.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>10457251.0</v>
+        <v>10124730.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>11519828.0</v>
+        <v>11151670.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>12627392.0</v>
+        <v>12222136.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>13781869.0</v>
+        <v>13337863.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>14985265.0</v>
+        <v>14500920.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>16239574.0</v>
+        <v>15713194.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>17547056.0</v>
+        <v>16976832.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>18909867.0</v>
+        <v>18293967.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>20330443.0</v>
+        <v>19666919.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>21811198.0</v>
+        <v>21097988.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>23354753.0</v>
+        <v>22589765.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>24963609.0</v>
+        <v>24144725.0</v>
       </c>
     </row>
   </sheetData>
@@ -2113,75 +2112,75 @@
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>169284.0</v>
+        <v>137943.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>176458.0</v>
+        <v>170544.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>183929.0</v>
+        <v>177762.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>191741.0</v>
+        <v>185301.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>199861.0</v>
+        <v>193161.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>208311.0</v>
+        <v>201330.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>217140.0</v>
+        <v>209856.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>226329.0</v>
+        <v>218738.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>235911.0</v>
+        <v>228009.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>245904.0</v>
+        <v>237650.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>256323.0</v>
+        <v>247731.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>267168.0</v>
+        <v>258214.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>278494.0</v>
+        <v>269155.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>290279.0</v>
+        <v>280550.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>302583.0</v>
+        <v>292439.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>315401.0</v>
+        <v>304818.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>328777.0</v>
+        <v>317749.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>342686.0</v>
+        <v>331206.0</v>
       </c>
     </row>
     <row r="11">
@@ -2216,75 +2215,75 @@
       </c>
       <c r="I11">
         <f>ROUND(Revenue!I15*Assumptions!$B$16,0)</f>
-        <v>76059.0</v>
+        <v>61977.0</v>
       </c>
       <c r="J11">
         <f>ROUND(Revenue!J15*Assumptions!$B$16,0)</f>
-        <v>79282.0</v>
+        <v>76625.0</v>
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>82638.0</v>
+        <v>79868.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>86148.0</v>
+        <v>83255.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>89797.0</v>
+        <v>86786.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>93593.0</v>
+        <v>90457.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>97560.0</v>
+        <v>94287.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>101689.0</v>
+        <v>98278.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>105994.0</v>
+        <v>102444.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>110483.0</v>
+        <v>106775.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>115165.0</v>
+        <v>111305.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>120037.0</v>
+        <v>116015.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>125126.0</v>
+        <v>120930.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>130421.0</v>
+        <v>126050.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>135949.0</v>
+        <v>131392.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>141708.0</v>
+        <v>136953.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>147718.0</v>
+        <v>142763.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>153968.0</v>
+        <v>148810.0</v>
       </c>
     </row>
     <row r="12">
@@ -2422,75 +2421,75 @@
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>537276.0</v>
+        <v>491853.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>569392.0</v>
+        <v>560821.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>601939.0</v>
+        <v>593002.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>634981.0</v>
+        <v>625648.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>668473.0</v>
+        <v>658762.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>702443.0</v>
+        <v>692326.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>736963.0</v>
+        <v>726406.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>772007.0</v>
+        <v>761005.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>807621.0</v>
+        <v>796169.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>843830.0</v>
+        <v>831868.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>880661.0</v>
+        <v>868209.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>918109.0</v>
+        <v>905133.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>956256.0</v>
+        <v>942721.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>995068.0</v>
+        <v>980968.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>1034634.0</v>
+        <v>1019933.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>1074947.0</v>
+        <v>1059609.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>1116069.0</v>
+        <v>1100086.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>1157966.0</v>
+        <v>1141328.0</v>
       </c>
     </row>
   </sheetData>
@@ -2654,79 +2653,79 @@
       </c>
       <c r="I5">
         <f>Revenue!I15</f>
-        <v>794761.0</v>
+        <v>647621.0</v>
       </c>
       <c r="J5">
         <f>Revenue!J15</f>
-        <v>828442.0</v>
+        <v>800678.0</v>
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>863515.0</v>
+        <v>834565.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>900193.0</v>
+        <v>869956.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>938315.0</v>
+        <v>906858.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>977986.0</v>
+        <v>945211.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>1019436.0</v>
+        <v>985238.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>1062577.0</v>
+        <v>1026940.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>1107564.0</v>
+        <v>1070466.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>1154477.0</v>
+        <v>1115727.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>1203396.0</v>
+        <v>1163057.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>1254309.0</v>
+        <v>1212274.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>1307482.0</v>
+        <v>1263638.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>1362811.0</v>
+        <v>1317135.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>1420576.0</v>
+        <v>1372952.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>1480755.0</v>
+        <v>1431069.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>1543555.0</v>
+        <v>1491777.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>1608856.0</v>
+        <v>1554960.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>24963609.0</v>
+        <v>24144725.0</v>
       </c>
     </row>
     <row r="6">
@@ -2761,79 +2760,79 @@
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-169284.0</v>
+        <v>-137943.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-176458.0</v>
+        <v>-170544.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-183929.0</v>
+        <v>-177762.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-191741.0</v>
+        <v>-185301.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-199861.0</v>
+        <v>-193161.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-208311.0</v>
+        <v>-201330.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-217140.0</v>
+        <v>-209856.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-226329.0</v>
+        <v>-218738.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-235911.0</v>
+        <v>-228009.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-245904.0</v>
+        <v>-237650.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-256323.0</v>
+        <v>-247731.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-267168.0</v>
+        <v>-258214.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-278494.0</v>
+        <v>-269155.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-290279.0</v>
+        <v>-280550.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-302583.0</v>
+        <v>-292439.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-315401.0</v>
+        <v>-304818.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-328777.0</v>
+        <v>-317749.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-342686.0</v>
+        <v>-331206.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-5317249.0</v>
+        <v>-5142826.0</v>
       </c>
     </row>
     <row r="7">
@@ -2868,79 +2867,79 @@
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>625477.0</v>
+        <v>509678.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>651984.0</v>
+        <v>630134.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>679586.0</v>
+        <v>656803.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>708452.0</v>
+        <v>684655.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>738454.0</v>
+        <v>713697.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>769675.0</v>
+        <v>743881.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>802296.0</v>
+        <v>775382.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>836248.0</v>
+        <v>808202.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>871653.0</v>
+        <v>842457.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>908573.0</v>
+        <v>878077.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>947073.0</v>
+        <v>915326.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>987141.0</v>
+        <v>954060.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>1028988.0</v>
+        <v>994483.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>1072532.0</v>
+        <v>1036585.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>1117993.0</v>
+        <v>1080513.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>1165354.0</v>
+        <v>1126251.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>1214778.0</v>
+        <v>1174028.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>1266170.0</v>
+        <v>1223754.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>19646360.0</v>
+        <v>19001899.0</v>
       </c>
     </row>
     <row r="8">
@@ -3185,79 +3184,79 @@
       </c>
       <c r="I11">
         <f>-Costs!I11</f>
-        <v>-76059.0</v>
+        <v>-61977.0</v>
       </c>
       <c r="J11">
         <f>-Costs!J11</f>
-        <v>-79282.0</v>
+        <v>-76625.0</v>
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-82638.0</v>
+        <v>-79868.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-86148.0</v>
+        <v>-83255.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-89797.0</v>
+        <v>-86786.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-93593.0</v>
+        <v>-90457.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-97560.0</v>
+        <v>-94287.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-101689.0</v>
+        <v>-98278.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-105994.0</v>
+        <v>-102444.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-110483.0</v>
+        <v>-106775.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-115165.0</v>
+        <v>-111305.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-120037.0</v>
+        <v>-116015.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-125126.0</v>
+        <v>-120930.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-130421.0</v>
+        <v>-126050.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-135949.0</v>
+        <v>-131392.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-141708.0</v>
+        <v>-136953.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-147718.0</v>
+        <v>-142763.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-153968.0</v>
+        <v>-148810.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-2389018.0</v>
+        <v>-2310653.0</v>
       </c>
     </row>
     <row r="12">
@@ -3399,79 +3398,79 @@
       </c>
       <c r="I13">
         <f>I10+I11+I12</f>
-        <v>-367992.0</v>
+        <v>-353910.0</v>
       </c>
       <c r="J13">
         <f>J10+J11+J12</f>
-        <v>-392934.0</v>
+        <v>-390277.0</v>
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-418010.0</v>
+        <v>-415240.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-443240.0</v>
+        <v>-440347.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-468612.0</v>
+        <v>-465601.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-494132.0</v>
+        <v>-490996.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-519823.0</v>
+        <v>-516550.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-545678.0</v>
+        <v>-542267.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-571710.0</v>
+        <v>-568160.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-597926.0</v>
+        <v>-594218.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-624338.0</v>
+        <v>-620478.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-650941.0</v>
+        <v>-646919.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-677762.0</v>
+        <v>-673566.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-704789.0</v>
+        <v>-700418.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-732051.0</v>
+        <v>-727494.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-759546.0</v>
+        <v>-754791.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-787292.0</v>
+        <v>-782337.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-815280.0</v>
+        <v>-810122.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-12263303.0</v>
+        <v>-12184938.0</v>
       </c>
     </row>
     <row r="15">
@@ -3506,79 +3505,79 @@
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>257485.0</v>
+        <v>155768.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>259050.0</v>
+        <v>239857.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>261576.0</v>
+        <v>241563.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>265212.0</v>
+        <v>244308.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>269842.0</v>
+        <v>248096.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>275543.0</v>
+        <v>252885.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>282473.0</v>
+        <v>258832.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>290570.0</v>
+        <v>265935.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>299943.0</v>
+        <v>274297.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>310647.0</v>
+        <v>283859.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>322735.0</v>
+        <v>294848.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>336200.0</v>
+        <v>307141.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>351226.0</v>
+        <v>320917.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>367743.0</v>
+        <v>336167.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>385942.0</v>
+        <v>353019.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>405808.0</v>
+        <v>371460.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>427486.0</v>
+        <v>391691.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>450890.0</v>
+        <v>413632.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>7383057.0</v>
+        <v>6816961.0</v>
       </c>
     </row>
     <row r="16">
@@ -3613,75 +3612,75 @@
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.324</v>
+        <v>0.2405</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.3127</v>
+        <v>0.2996</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.3029</v>
+        <v>0.2894</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.2946</v>
+        <v>0.2808</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.2876</v>
+        <v>0.2736</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.2817</v>
+        <v>0.2675</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.2771</v>
+        <v>0.2627</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.2735</v>
+        <v>0.259</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.2708</v>
+        <v>0.2562</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.2691</v>
+        <v>0.2544</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.2682</v>
+        <v>0.2535</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.268</v>
+        <v>0.2534</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.2686</v>
+        <v>0.254</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.2698</v>
+        <v>0.2552</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.2717</v>
+        <v>0.2571</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.2741</v>
+        <v>0.2596</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.2769</v>
+        <v>0.2626</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.2803</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="18">
@@ -3716,75 +3715,75 @@
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>1820171.0</v>
+        <v>1718454.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>2079221.0</v>
+        <v>1958311.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>2340797.0</v>
+        <v>2199874.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>2606009.0</v>
+        <v>2444182.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>2875851.0</v>
+        <v>2692278.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>3151394.0</v>
+        <v>2945163.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>3433867.0</v>
+        <v>3203995.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>3724437.0</v>
+        <v>3469930.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>4024380.0</v>
+        <v>3744227.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>4335027.0</v>
+        <v>4028086.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>4657762.0</v>
+        <v>4322934.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>4993962.0</v>
+        <v>4630075.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>5345188.0</v>
+        <v>4950992.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>5712931.0</v>
+        <v>5287159.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>6098873.0</v>
+        <v>5640178.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>6504681.0</v>
+        <v>6011638.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>6932167.0</v>
+        <v>6403329.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>7383057.0</v>
+        <v>6816961.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3815,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>24963609.0</v>
+        <v>24144725.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3826,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>7383057.0</v>
+        <v>6816961.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3837,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>4231663.0</v>
+        <v>3871798.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3859,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>55011619.0</v>
+        <v>50333374.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3881,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>51411619.0</v>
+        <v>46733374.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>307627.375</v>
+        <v>284040.0416666667</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3903,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>450890.0</v>
+        <v>413632.0</v>
       </c>
     </row>
     <row r="13">
@@ -3915,7 +3914,7 @@
       </c>
       <c r="B13">
         <f>MIN('P&amp;L'!C15:Z15)</f>
-        <v>256931.0</v>
+        <v>155768.0</v>
       </c>
     </row>
     <row r="14">
@@ -3926,7 +3925,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>7383057.0</v>
+        <v>6816961.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3936,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>193959.0</v>
+        <v>257864.0</v>
       </c>
     </row>
   </sheetData>
